--- a/output/yearly_population_iteration_21_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_21_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5646</v>
+        <v>5984</v>
       </c>
       <c r="C2" t="n">
-        <v>10364</v>
+        <v>7588</v>
       </c>
       <c r="D2" t="n">
-        <v>24079</v>
+        <v>26529</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3230</v>
+        <v>3762</v>
       </c>
       <c r="C3" t="n">
-        <v>4710</v>
+        <v>3708</v>
       </c>
       <c r="D3" t="n">
-        <v>14551</v>
+        <v>16269</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2650</v>
+        <v>2676</v>
       </c>
       <c r="C4" t="n">
-        <v>3683</v>
+        <v>4182</v>
       </c>
       <c r="D4" t="n">
-        <v>7900</v>
+        <v>7485</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1714</v>
+        <v>1688</v>
       </c>
       <c r="C5" t="n">
-        <v>3462</v>
+        <v>3950</v>
       </c>
       <c r="D5" t="n">
-        <v>3129</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>970</v>
+        <v>1014</v>
       </c>
       <c r="C6" t="n">
-        <v>2570</v>
+        <v>2855</v>
       </c>
       <c r="D6" t="n">
-        <v>1288</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>464</v>
+        <v>499</v>
       </c>
       <c r="C7" t="n">
-        <v>1564</v>
+        <v>1765</v>
       </c>
       <c r="D7" t="n">
-        <v>672</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="C8" t="n">
-        <v>691</v>
+        <v>881</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>388</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -968,7 +968,7 @@
         <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7534</v>
+        <v>6335</v>
       </c>
       <c r="C2" t="n">
-        <v>8933</v>
+        <v>9546</v>
       </c>
       <c r="D2" t="n">
-        <v>24113</v>
+        <v>26281</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3510</v>
+        <v>3869</v>
       </c>
       <c r="C3" t="n">
-        <v>6527</v>
+        <v>4840</v>
       </c>
       <c r="D3" t="n">
-        <v>15061</v>
+        <v>16571</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2492</v>
+        <v>2691</v>
       </c>
       <c r="C4" t="n">
-        <v>4073</v>
+        <v>3862</v>
       </c>
       <c r="D4" t="n">
-        <v>8669</v>
+        <v>8619</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1898</v>
+        <v>1886</v>
       </c>
       <c r="C5" t="n">
-        <v>3496</v>
+        <v>3939</v>
       </c>
       <c r="D5" t="n">
-        <v>3812</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1180</v>
+        <v>1189</v>
       </c>
       <c r="C6" t="n">
-        <v>2930</v>
+        <v>3331</v>
       </c>
       <c r="D6" t="n">
-        <v>1540</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>615</v>
+        <v>646</v>
       </c>
       <c r="C7" t="n">
-        <v>2026</v>
+        <v>2238</v>
       </c>
       <c r="D7" t="n">
-        <v>761</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="C8" t="n">
-        <v>1068</v>
+        <v>1270</v>
       </c>
       <c r="D8" t="n">
-        <v>466</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C9" t="n">
-        <v>472</v>
+        <v>591</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>247</v>
+        <v>288</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
         <v>209</v>
@@ -1237,7 +1237,7 @@
         <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1307,7 +1307,7 @@
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7739</v>
+        <v>6618</v>
       </c>
       <c r="C2" t="n">
-        <v>9690</v>
+        <v>15184</v>
       </c>
       <c r="D2" t="n">
-        <v>27335</v>
+        <v>37242</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4174</v>
+        <v>3987</v>
       </c>
       <c r="C3" t="n">
-        <v>6679</v>
+        <v>6021</v>
       </c>
       <c r="D3" t="n">
-        <v>15231</v>
+        <v>16726</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2482</v>
+        <v>2730</v>
       </c>
       <c r="C4" t="n">
-        <v>5056</v>
+        <v>4176</v>
       </c>
       <c r="D4" t="n">
-        <v>9304</v>
+        <v>9578</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1911</v>
+        <v>1963</v>
       </c>
       <c r="C5" t="n">
-        <v>3678</v>
+        <v>3785</v>
       </c>
       <c r="D5" t="n">
-        <v>4442</v>
+        <v>3951</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="C6" t="n">
-        <v>3113</v>
+        <v>3557</v>
       </c>
       <c r="D6" t="n">
-        <v>1831</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>767</v>
+        <v>778</v>
       </c>
       <c r="C7" t="n">
-        <v>2386</v>
+        <v>2665</v>
       </c>
       <c r="D7" t="n">
-        <v>867</v>
+        <v>776</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="C8" t="n">
-        <v>1461</v>
+        <v>1658</v>
       </c>
       <c r="D8" t="n">
-        <v>497</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C9" t="n">
-        <v>700</v>
+        <v>844</v>
       </c>
       <c r="D9" t="n">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>332</v>
+        <v>397</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7053</v>
+        <v>6152</v>
       </c>
       <c r="C2" t="n">
-        <v>6434</v>
+        <v>10203</v>
       </c>
       <c r="D2" t="n">
-        <v>22234</v>
+        <v>30435</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4817</v>
+        <v>4873</v>
       </c>
       <c r="C3" t="n">
-        <v>9719</v>
+        <v>9407</v>
       </c>
       <c r="D3" t="n">
-        <v>17024</v>
+        <v>18265</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1765</v>
+        <v>1813</v>
       </c>
       <c r="C4" t="n">
-        <v>6394</v>
+        <v>5958</v>
       </c>
       <c r="D4" t="n">
-        <v>9190</v>
+        <v>9037</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="C5" t="n">
-        <v>3050</v>
+        <v>3485</v>
       </c>
       <c r="D5" t="n">
-        <v>3031</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="C6" t="n">
-        <v>2338</v>
+        <v>2611</v>
       </c>
       <c r="D6" t="n">
-        <v>849</v>
+        <v>760</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="C7" t="n">
-        <v>1431</v>
+        <v>1624</v>
       </c>
       <c r="D7" t="n">
-        <v>487</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C8" t="n">
-        <v>686</v>
+        <v>827</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4267</v>
+        <v>3815</v>
       </c>
       <c r="C2" t="n">
-        <v>3207</v>
+        <v>4380</v>
       </c>
       <c r="D2" t="n">
-        <v>15575</v>
+        <v>22273</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4981</v>
+        <v>4716</v>
       </c>
       <c r="C3" t="n">
-        <v>7393</v>
+        <v>8850</v>
       </c>
       <c r="D3" t="n">
-        <v>16929</v>
+        <v>18868</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2549</v>
+        <v>2611</v>
       </c>
       <c r="C4" t="n">
-        <v>8102</v>
+        <v>7685</v>
       </c>
       <c r="D4" t="n">
-        <v>10290</v>
+        <v>10353</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1367</v>
+        <v>1370</v>
       </c>
       <c r="C5" t="n">
-        <v>4545</v>
+        <v>4600</v>
       </c>
       <c r="D5" t="n">
-        <v>3765</v>
+        <v>3411</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C6" t="n">
-        <v>2710</v>
+        <v>3046</v>
       </c>
       <c r="D6" t="n">
-        <v>1073</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="C7" t="n">
-        <v>1814</v>
+        <v>2037</v>
       </c>
       <c r="D7" t="n">
-        <v>535</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C8" t="n">
-        <v>910</v>
+        <v>1075</v>
       </c>
       <c r="D8" t="n">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>385</v>
+        <v>446</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5512</v>
+        <v>3528</v>
       </c>
       <c r="C2" t="n">
-        <v>11048</v>
+        <v>9286</v>
       </c>
       <c r="D2" t="n">
-        <v>15819</v>
+        <v>19559</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3920</v>
+        <v>3642</v>
       </c>
       <c r="C3" t="n">
-        <v>4695</v>
+        <v>5900</v>
       </c>
       <c r="D3" t="n">
-        <v>15569</v>
+        <v>18241</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3127</v>
+        <v>3044</v>
       </c>
       <c r="C4" t="n">
-        <v>7650</v>
+        <v>8180</v>
       </c>
       <c r="D4" t="n">
-        <v>11124</v>
+        <v>11427</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1664</v>
+        <v>1677</v>
       </c>
       <c r="C5" t="n">
-        <v>6157</v>
+        <v>5955</v>
       </c>
       <c r="D5" t="n">
-        <v>4715</v>
+        <v>4340</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="C6" t="n">
-        <v>3555</v>
+        <v>3717</v>
       </c>
       <c r="D6" t="n">
-        <v>1472</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="C7" t="n">
-        <v>2208</v>
+        <v>2501</v>
       </c>
       <c r="D7" t="n">
-        <v>608</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>1299</v>
+        <v>1481</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>598</v>
+        <v>694</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="D10" t="n">
         <v>216</v>
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>24</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3208</v>
+        <v>2115</v>
       </c>
       <c r="C2" t="n">
-        <v>4994</v>
+        <v>4250</v>
       </c>
       <c r="D2" t="n">
-        <v>10894</v>
+        <v>13497</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4161</v>
+        <v>3487</v>
       </c>
       <c r="C3" t="n">
-        <v>6773</v>
+        <v>6875</v>
       </c>
       <c r="D3" t="n">
-        <v>15223</v>
+        <v>17950</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3457</v>
+        <v>3337</v>
       </c>
       <c r="C4" t="n">
-        <v>7277</v>
+        <v>8107</v>
       </c>
       <c r="D4" t="n">
-        <v>11746</v>
+        <v>12433</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="C5" t="n">
-        <v>7325</v>
+        <v>7283</v>
       </c>
       <c r="D5" t="n">
-        <v>5097</v>
+        <v>4595</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="C6" t="n">
-        <v>4429</v>
+        <v>4587</v>
       </c>
       <c r="D6" t="n">
-        <v>1441</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>2345</v>
+        <v>2653</v>
       </c>
       <c r="D7" t="n">
-        <v>608</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1006</v>
+        <v>1144</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>23</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3223</v>
+        <v>2846</v>
       </c>
       <c r="C2" t="n">
-        <v>4557</v>
+        <v>8382</v>
       </c>
       <c r="D2" t="n">
-        <v>9576</v>
+        <v>16687</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3204</v>
+        <v>2505</v>
       </c>
       <c r="C3" t="n">
-        <v>5288</v>
+        <v>5034</v>
       </c>
       <c r="D3" t="n">
-        <v>13611</v>
+        <v>16138</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3273</v>
+        <v>2978</v>
       </c>
       <c r="C4" t="n">
-        <v>6883</v>
+        <v>7424</v>
       </c>
       <c r="D4" t="n">
-        <v>11956</v>
+        <v>12955</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2171</v>
+        <v>2123</v>
       </c>
       <c r="C5" t="n">
-        <v>7220</v>
+        <v>7573</v>
       </c>
       <c r="D5" t="n">
-        <v>5963</v>
+        <v>5703</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1096</v>
+        <v>1086</v>
       </c>
       <c r="C6" t="n">
-        <v>5681</v>
+        <v>5728</v>
       </c>
       <c r="D6" t="n">
-        <v>1962</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C7" t="n">
-        <v>3247</v>
+        <v>3481</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>671</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C8" t="n">
-        <v>1523</v>
+        <v>1713</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>527</v>
+        <v>582</v>
       </c>
       <c r="D9" t="n">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2375</v>
+        <v>2105</v>
       </c>
       <c r="C2" t="n">
-        <v>3623</v>
+        <v>4469</v>
       </c>
       <c r="D2" t="n">
-        <v>8267</v>
+        <v>12796</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2811</v>
+        <v>2290</v>
       </c>
       <c r="C3" t="n">
-        <v>4570</v>
+        <v>5820</v>
       </c>
       <c r="D3" t="n">
-        <v>12386</v>
+        <v>15325</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2993</v>
+        <v>2593</v>
       </c>
       <c r="C4" t="n">
-        <v>6213</v>
+        <v>6448</v>
       </c>
       <c r="D4" t="n">
-        <v>11929</v>
+        <v>13113</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2366</v>
+        <v>2290</v>
       </c>
       <c r="C5" t="n">
-        <v>7220</v>
+        <v>7651</v>
       </c>
       <c r="D5" t="n">
-        <v>6586</v>
+        <v>6474</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1304</v>
+        <v>1272</v>
       </c>
       <c r="C6" t="n">
-        <v>6407</v>
+        <v>6536</v>
       </c>
       <c r="D6" t="n">
-        <v>2322</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C7" t="n">
-        <v>4088</v>
+        <v>4268</v>
       </c>
       <c r="D7" t="n">
-        <v>802</v>
+        <v>763</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>1964</v>
+        <v>2169</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>630</v>
+        <v>674</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
         <v>177</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>136</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3374</v>
+        <v>2890</v>
       </c>
       <c r="C2" t="n">
-        <v>12681</v>
+        <v>5458</v>
       </c>
       <c r="D2" t="n">
-        <v>15218</v>
+        <v>17894</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2230</v>
+        <v>1871</v>
       </c>
       <c r="C3" t="n">
-        <v>3746</v>
+        <v>4737</v>
       </c>
       <c r="D3" t="n">
-        <v>11099</v>
+        <v>14040</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2569</v>
+        <v>2182</v>
       </c>
       <c r="C4" t="n">
-        <v>5373</v>
+        <v>6048</v>
       </c>
       <c r="D4" t="n">
-        <v>11632</v>
+        <v>13032</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2353</v>
+        <v>2189</v>
       </c>
       <c r="C5" t="n">
-        <v>6654</v>
+        <v>7006</v>
       </c>
       <c r="D5" t="n">
-        <v>7040</v>
+        <v>7169</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1555</v>
+        <v>1502</v>
       </c>
       <c r="C6" t="n">
-        <v>6671</v>
+        <v>6909</v>
       </c>
       <c r="D6" t="n">
-        <v>2864</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>560</v>
+        <v>539</v>
       </c>
       <c r="C7" t="n">
-        <v>4972</v>
+        <v>5110</v>
       </c>
       <c r="D7" t="n">
-        <v>987</v>
+        <v>901</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>2752</v>
+        <v>2929</v>
       </c>
       <c r="D8" t="n">
-        <v>473</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1080</v>
+        <v>1163</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="D10" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5545</v>
+        <v>6829</v>
       </c>
       <c r="C2" t="n">
-        <v>4552</v>
+        <v>7593</v>
       </c>
       <c r="D2" t="n">
-        <v>17221</v>
+        <v>6559</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2416</v>
+        <v>2068</v>
       </c>
       <c r="C2" t="n">
-        <v>7202</v>
+        <v>3144</v>
       </c>
       <c r="D2" t="n">
-        <v>11201</v>
+        <v>13169</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3006</v>
+        <v>2554</v>
       </c>
       <c r="C3" t="n">
-        <v>6142</v>
+        <v>5315</v>
       </c>
       <c r="D3" t="n">
-        <v>12410</v>
+        <v>15499</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3487</v>
+        <v>3114</v>
       </c>
       <c r="C4" t="n">
-        <v>7597</v>
+        <v>8480</v>
       </c>
       <c r="D4" t="n">
-        <v>12007</v>
+        <v>13355</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1502</v>
+        <v>1448</v>
       </c>
       <c r="C5" t="n">
-        <v>9508</v>
+        <v>9922</v>
       </c>
       <c r="D5" t="n">
-        <v>6539</v>
+        <v>6433</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>517</v>
+        <v>498</v>
       </c>
       <c r="C6" t="n">
-        <v>6245</v>
+        <v>6361</v>
       </c>
       <c r="D6" t="n">
-        <v>2244</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>2696</v>
+        <v>2870</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1058</v>
+        <v>1139</v>
       </c>
       <c r="D8" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="D9" t="n">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6347</v>
+        <v>6524</v>
       </c>
       <c r="C2" t="n">
-        <v>3744</v>
+        <v>6295</v>
       </c>
       <c r="D2" t="n">
-        <v>18988</v>
+        <v>16175</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2356</v>
+        <v>2901</v>
       </c>
       <c r="C3" t="n">
-        <v>2294</v>
+        <v>3826</v>
       </c>
       <c r="D3" t="n">
-        <v>3532</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4003</v>
+        <v>4200</v>
       </c>
       <c r="C2" t="n">
-        <v>9183</v>
+        <v>3939</v>
       </c>
       <c r="D2" t="n">
-        <v>15581</v>
+        <v>20664</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3573</v>
+        <v>3872</v>
       </c>
       <c r="C3" t="n">
-        <v>2685</v>
+        <v>4504</v>
       </c>
       <c r="D3" t="n">
-        <v>5868</v>
+        <v>4037</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1057</v>
+        <v>1294</v>
       </c>
       <c r="C4" t="n">
-        <v>1388</v>
+        <v>2285</v>
       </c>
       <c r="D4" t="n">
-        <v>1893</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
         <v>1186</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4927</v>
+        <v>4801</v>
       </c>
       <c r="C2" t="n">
-        <v>4855</v>
+        <v>6793</v>
       </c>
       <c r="D2" t="n">
-        <v>30002</v>
+        <v>19568</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3121</v>
+        <v>3328</v>
       </c>
       <c r="C3" t="n">
-        <v>5391</v>
+        <v>3631</v>
       </c>
       <c r="D3" t="n">
-        <v>6999</v>
+        <v>6406</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1959</v>
+        <v>2200</v>
       </c>
       <c r="C4" t="n">
-        <v>2093</v>
+        <v>3494</v>
       </c>
       <c r="D4" t="n">
-        <v>2598</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>495</v>
+        <v>580</v>
       </c>
       <c r="C5" t="n">
-        <v>852</v>
+        <v>1344</v>
       </c>
       <c r="D5" t="n">
-        <v>1267</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5280,7 +5280,7 @@
         <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5508</v>
+        <v>5108</v>
       </c>
       <c r="C2" t="n">
-        <v>4487</v>
+        <v>7199</v>
       </c>
       <c r="D2" t="n">
-        <v>31280</v>
+        <v>26120</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3261</v>
+        <v>3307</v>
       </c>
       <c r="C3" t="n">
-        <v>4452</v>
+        <v>4576</v>
       </c>
       <c r="D3" t="n">
-        <v>10002</v>
+        <v>7955</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2167</v>
+        <v>2363</v>
       </c>
       <c r="C4" t="n">
-        <v>3802</v>
+        <v>3494</v>
       </c>
       <c r="D4" t="n">
-        <v>3321</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1007</v>
+        <v>1143</v>
       </c>
       <c r="C5" t="n">
-        <v>1489</v>
+        <v>2417</v>
       </c>
       <c r="D5" t="n">
-        <v>1446</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>280</v>
+        <v>315</v>
       </c>
       <c r="C6" t="n">
-        <v>578</v>
+        <v>827</v>
       </c>
       <c r="D6" t="n">
-        <v>963</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5591,7 +5591,7 @@
         <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5709</v>
+        <v>5797</v>
       </c>
       <c r="C2" t="n">
-        <v>6051</v>
+        <v>6670</v>
       </c>
       <c r="D2" t="n">
-        <v>28139</v>
+        <v>34444</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3203</v>
+        <v>3039</v>
       </c>
       <c r="C3" t="n">
-        <v>3661</v>
+        <v>4846</v>
       </c>
       <c r="D3" t="n">
-        <v>11789</v>
+        <v>9554</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1673</v>
+        <v>1749</v>
       </c>
       <c r="C4" t="n">
-        <v>3379</v>
+        <v>3324</v>
       </c>
       <c r="D4" t="n">
-        <v>3845</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>829</v>
+        <v>924</v>
       </c>
       <c r="C5" t="n">
-        <v>1986</v>
+        <v>2180</v>
       </c>
       <c r="D5" t="n">
-        <v>1414</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="C6" t="n">
-        <v>695</v>
+        <v>1097</v>
       </c>
       <c r="D6" t="n">
-        <v>795</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>297</v>
+        <v>372</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5916,7 +5916,7 @@
         <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5427</v>
+        <v>5695</v>
       </c>
       <c r="C2" t="n">
-        <v>4084</v>
+        <v>4193</v>
       </c>
       <c r="D2" t="n">
-        <v>21266</v>
+        <v>33524</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3703</v>
+        <v>3674</v>
       </c>
       <c r="C3" t="n">
-        <v>4363</v>
+        <v>5089</v>
       </c>
       <c r="D3" t="n">
-        <v>13780</v>
+        <v>13307</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2130</v>
+        <v>2102</v>
       </c>
       <c r="C4" t="n">
-        <v>3481</v>
+        <v>4189</v>
       </c>
       <c r="D4" t="n">
-        <v>5405</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1124</v>
+        <v>1186</v>
       </c>
       <c r="C5" t="n">
-        <v>2773</v>
+        <v>2815</v>
       </c>
       <c r="D5" t="n">
-        <v>1861</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>530</v>
+        <v>591</v>
       </c>
       <c r="C6" t="n">
-        <v>1429</v>
+        <v>1707</v>
       </c>
       <c r="D6" t="n">
-        <v>894</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="C7" t="n">
-        <v>523</v>
+        <v>783</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>263</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4092</v>
+        <v>5439</v>
       </c>
       <c r="C2" t="n">
-        <v>7087</v>
+        <v>4518</v>
       </c>
       <c r="D2" t="n">
-        <v>24188</v>
+        <v>27317</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3748</v>
+        <v>3828</v>
       </c>
       <c r="C3" t="n">
-        <v>3635</v>
+        <v>3982</v>
       </c>
       <c r="D3" t="n">
-        <v>13985</v>
+        <v>15583</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2521</v>
+        <v>2465</v>
       </c>
       <c r="C4" t="n">
-        <v>3916</v>
+        <v>4611</v>
       </c>
       <c r="D4" t="n">
-        <v>6796</v>
+        <v>5898</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1421</v>
+        <v>1451</v>
       </c>
       <c r="C5" t="n">
-        <v>3109</v>
+        <v>3481</v>
       </c>
       <c r="D5" t="n">
-        <v>2484</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>757</v>
+        <v>804</v>
       </c>
       <c r="C6" t="n">
-        <v>2120</v>
+        <v>2282</v>
       </c>
       <c r="D6" t="n">
-        <v>1057</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>314</v>
+        <v>351</v>
       </c>
       <c r="C7" t="n">
-        <v>1011</v>
+        <v>1271</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>397</v>
+        <v>547</v>
       </c>
       <c r="D8" t="n">
         <v>413</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">

--- a/output/yearly_population_iteration_21_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_21_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5984</v>
+        <v>6767</v>
       </c>
       <c r="C2" t="n">
-        <v>7588</v>
+        <v>13585</v>
       </c>
       <c r="D2" t="n">
-        <v>26529</v>
+        <v>28623</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3762</v>
+        <v>4070</v>
       </c>
       <c r="C3" t="n">
-        <v>3708</v>
+        <v>5200</v>
       </c>
       <c r="D3" t="n">
-        <v>16269</v>
+        <v>15939</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2676</v>
+        <v>2888</v>
       </c>
       <c r="C4" t="n">
-        <v>4182</v>
+        <v>5311</v>
       </c>
       <c r="D4" t="n">
-        <v>7485</v>
+        <v>7545</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1688</v>
+        <v>1917</v>
       </c>
       <c r="C5" t="n">
-        <v>3950</v>
+        <v>4616</v>
       </c>
       <c r="D5" t="n">
-        <v>2605</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1014</v>
+        <v>1117</v>
       </c>
       <c r="C6" t="n">
-        <v>2855</v>
+        <v>3679</v>
       </c>
       <c r="D6" t="n">
-        <v>1096</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="C7" t="n">
-        <v>1765</v>
+        <v>2470</v>
       </c>
       <c r="D7" t="n">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C8" t="n">
-        <v>881</v>
+        <v>1190</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>388</v>
+        <v>454</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6335</v>
+        <v>6721</v>
       </c>
       <c r="C2" t="n">
-        <v>9546</v>
+        <v>12777</v>
       </c>
       <c r="D2" t="n">
-        <v>26281</v>
+        <v>29850</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3869</v>
+        <v>4246</v>
       </c>
       <c r="C3" t="n">
-        <v>4840</v>
+        <v>7812</v>
       </c>
       <c r="D3" t="n">
-        <v>16571</v>
+        <v>16516</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2691</v>
+        <v>2912</v>
       </c>
       <c r="C4" t="n">
-        <v>3862</v>
+        <v>5149</v>
       </c>
       <c r="D4" t="n">
-        <v>8619</v>
+        <v>8532</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1886</v>
+        <v>2050</v>
       </c>
       <c r="C5" t="n">
-        <v>3939</v>
+        <v>4782</v>
       </c>
       <c r="D5" t="n">
-        <v>3322</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1189</v>
+        <v>1315</v>
       </c>
       <c r="C6" t="n">
-        <v>3331</v>
+        <v>4049</v>
       </c>
       <c r="D6" t="n">
-        <v>1302</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>646</v>
+        <v>683</v>
       </c>
       <c r="C7" t="n">
-        <v>2238</v>
+        <v>2954</v>
       </c>
       <c r="D7" t="n">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C8" t="n">
-        <v>1270</v>
+        <v>1716</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C9" t="n">
-        <v>591</v>
+        <v>737</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6618</v>
+        <v>8676</v>
       </c>
       <c r="C2" t="n">
-        <v>15184</v>
+        <v>13248</v>
       </c>
       <c r="D2" t="n">
-        <v>37242</v>
+        <v>40760</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3987</v>
+        <v>4250</v>
       </c>
       <c r="C3" t="n">
-        <v>6021</v>
+        <v>8670</v>
       </c>
       <c r="D3" t="n">
-        <v>16726</v>
+        <v>17059</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2730</v>
+        <v>2914</v>
       </c>
       <c r="C4" t="n">
-        <v>4176</v>
+        <v>6091</v>
       </c>
       <c r="D4" t="n">
-        <v>9578</v>
+        <v>9422</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1963</v>
+        <v>2118</v>
       </c>
       <c r="C5" t="n">
-        <v>3785</v>
+        <v>4830</v>
       </c>
       <c r="D5" t="n">
-        <v>3951</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1341</v>
+        <v>1470</v>
       </c>
       <c r="C6" t="n">
-        <v>3557</v>
+        <v>4256</v>
       </c>
       <c r="D6" t="n">
-        <v>1575</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="7">
@@ -1472,10 +1472,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>778</v>
+        <v>824</v>
       </c>
       <c r="C7" t="n">
-        <v>2665</v>
+        <v>3342</v>
       </c>
       <c r="D7" t="n">
         <v>776</v>
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C8" t="n">
-        <v>1658</v>
+        <v>2159</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C9" t="n">
-        <v>844</v>
+        <v>1091</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>397</v>
+        <v>452</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
         <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6152</v>
+        <v>7963</v>
       </c>
       <c r="C2" t="n">
-        <v>10203</v>
+        <v>9326</v>
       </c>
       <c r="D2" t="n">
-        <v>30435</v>
+        <v>33426</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4873</v>
+        <v>5089</v>
       </c>
       <c r="C3" t="n">
-        <v>9407</v>
+        <v>12226</v>
       </c>
       <c r="D3" t="n">
-        <v>18265</v>
+        <v>18452</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1813</v>
+        <v>1957</v>
       </c>
       <c r="C4" t="n">
-        <v>5958</v>
+        <v>7852</v>
       </c>
       <c r="D4" t="n">
-        <v>9037</v>
+        <v>8906</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1239</v>
+        <v>1358</v>
       </c>
       <c r="C5" t="n">
-        <v>3485</v>
+        <v>4170</v>
       </c>
       <c r="D5" t="n">
-        <v>2643</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="6">
@@ -1769,10 +1769,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>718</v>
+        <v>761</v>
       </c>
       <c r="C6" t="n">
-        <v>2611</v>
+        <v>3275</v>
       </c>
       <c r="D6" t="n">
         <v>760</v>
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C7" t="n">
-        <v>1624</v>
+        <v>2115</v>
       </c>
       <c r="D7" t="n">
-        <v>474</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>827</v>
+        <v>1069</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>389</v>
+        <v>442</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3815</v>
+        <v>4716</v>
       </c>
       <c r="C2" t="n">
-        <v>4380</v>
+        <v>4280</v>
       </c>
       <c r="D2" t="n">
-        <v>22273</v>
+        <v>22746</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4716</v>
+        <v>5432</v>
       </c>
       <c r="C3" t="n">
-        <v>8850</v>
+        <v>9993</v>
       </c>
       <c r="D3" t="n">
-        <v>18868</v>
+        <v>19335</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2611</v>
+        <v>2671</v>
       </c>
       <c r="C4" t="n">
-        <v>7685</v>
+        <v>9846</v>
       </c>
       <c r="D4" t="n">
-        <v>10353</v>
+        <v>10180</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1370</v>
+        <v>1487</v>
       </c>
       <c r="C5" t="n">
-        <v>4600</v>
+        <v>5732</v>
       </c>
       <c r="D5" t="n">
-        <v>3411</v>
+        <v>3282</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>859</v>
+        <v>895</v>
       </c>
       <c r="C6" t="n">
-        <v>3046</v>
+        <v>3736</v>
       </c>
       <c r="D6" t="n">
-        <v>953</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C7" t="n">
-        <v>2037</v>
+        <v>2596</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>1075</v>
+        <v>1376</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>446</v>
+        <v>479</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3528</v>
+        <v>4743</v>
       </c>
       <c r="C2" t="n">
-        <v>9286</v>
+        <v>8790</v>
       </c>
       <c r="D2" t="n">
-        <v>19559</v>
+        <v>30446</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3642</v>
+        <v>4323</v>
       </c>
       <c r="C3" t="n">
-        <v>5900</v>
+        <v>6604</v>
       </c>
       <c r="D3" t="n">
-        <v>18241</v>
+        <v>18685</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3044</v>
+        <v>3284</v>
       </c>
       <c r="C4" t="n">
-        <v>8180</v>
+        <v>9710</v>
       </c>
       <c r="D4" t="n">
-        <v>11427</v>
+        <v>11179</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1677</v>
+        <v>1748</v>
       </c>
       <c r="C5" t="n">
-        <v>5955</v>
+        <v>7524</v>
       </c>
       <c r="D5" t="n">
-        <v>4340</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>987</v>
+        <v>1037</v>
       </c>
       <c r="C6" t="n">
-        <v>3717</v>
+        <v>4544</v>
       </c>
       <c r="D6" t="n">
-        <v>1317</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C7" t="n">
-        <v>2501</v>
+        <v>3089</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="C8" t="n">
-        <v>1481</v>
+        <v>1855</v>
       </c>
       <c r="D8" t="n">
-        <v>359</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>694</v>
+        <v>799</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
         <v>62</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2115</v>
+        <v>2877</v>
       </c>
       <c r="C2" t="n">
-        <v>4250</v>
+        <v>4321</v>
       </c>
       <c r="D2" t="n">
-        <v>13497</v>
+        <v>21263</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3487</v>
+        <v>4302</v>
       </c>
       <c r="C3" t="n">
-        <v>6875</v>
+        <v>7053</v>
       </c>
       <c r="D3" t="n">
-        <v>17950</v>
+        <v>19668</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3337</v>
+        <v>3558</v>
       </c>
       <c r="C4" t="n">
-        <v>8107</v>
+        <v>9579</v>
       </c>
       <c r="D4" t="n">
-        <v>12433</v>
+        <v>12033</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1750</v>
+        <v>1815</v>
       </c>
       <c r="C5" t="n">
-        <v>7283</v>
+        <v>9133</v>
       </c>
       <c r="D5" t="n">
-        <v>4595</v>
+        <v>4352</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C6" t="n">
-        <v>4587</v>
+        <v>5373</v>
       </c>
       <c r="D6" t="n">
-        <v>1290</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="C7" t="n">
-        <v>2653</v>
+        <v>3258</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1144</v>
+        <v>1310</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
         <v>97</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>60</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2846</v>
+        <v>3731</v>
       </c>
       <c r="C2" t="n">
-        <v>8382</v>
+        <v>7012</v>
       </c>
       <c r="D2" t="n">
-        <v>16687</v>
+        <v>24488</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2505</v>
+        <v>3206</v>
       </c>
       <c r="C3" t="n">
-        <v>5034</v>
+        <v>5247</v>
       </c>
       <c r="D3" t="n">
-        <v>16138</v>
+        <v>18581</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2978</v>
+        <v>3356</v>
       </c>
       <c r="C4" t="n">
-        <v>7424</v>
+        <v>8331</v>
       </c>
       <c r="D4" t="n">
-        <v>12955</v>
+        <v>12839</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2123</v>
+        <v>2204</v>
       </c>
       <c r="C5" t="n">
-        <v>7573</v>
+        <v>9131</v>
       </c>
       <c r="D5" t="n">
-        <v>5703</v>
+        <v>5367</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C6" t="n">
-        <v>5728</v>
+        <v>6947</v>
       </c>
       <c r="D6" t="n">
-        <v>1717</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="C7" t="n">
-        <v>3481</v>
+        <v>4076</v>
       </c>
       <c r="D7" t="n">
-        <v>671</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>1713</v>
+        <v>2003</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>582</v>
+        <v>622</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
         <v>60</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2105</v>
+        <v>2580</v>
       </c>
       <c r="C2" t="n">
-        <v>4469</v>
+        <v>4753</v>
       </c>
       <c r="D2" t="n">
-        <v>12796</v>
+        <v>18282</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2290</v>
+        <v>2951</v>
       </c>
       <c r="C3" t="n">
-        <v>5820</v>
+        <v>5428</v>
       </c>
       <c r="D3" t="n">
-        <v>15325</v>
+        <v>18261</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2593</v>
+        <v>3052</v>
       </c>
       <c r="C4" t="n">
-        <v>6448</v>
+        <v>7163</v>
       </c>
       <c r="D4" t="n">
-        <v>13113</v>
+        <v>13288</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2290</v>
+        <v>2384</v>
       </c>
       <c r="C5" t="n">
-        <v>7651</v>
+        <v>9022</v>
       </c>
       <c r="D5" t="n">
-        <v>6474</v>
+        <v>6095</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1272</v>
+        <v>1254</v>
       </c>
       <c r="C6" t="n">
-        <v>6536</v>
+        <v>7852</v>
       </c>
       <c r="D6" t="n">
-        <v>2074</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>304</v>
+        <v>268</v>
       </c>
       <c r="C7" t="n">
-        <v>4268</v>
+        <v>4972</v>
       </c>
       <c r="D7" t="n">
-        <v>763</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2169</v>
+        <v>2485</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>674</v>
+        <v>657</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2890</v>
+        <v>3265</v>
       </c>
       <c r="C2" t="n">
-        <v>5458</v>
+        <v>5362</v>
       </c>
       <c r="D2" t="n">
-        <v>17894</v>
+        <v>16517</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1871</v>
+        <v>2386</v>
       </c>
       <c r="C3" t="n">
-        <v>4737</v>
+        <v>4671</v>
       </c>
       <c r="D3" t="n">
-        <v>14040</v>
+        <v>17123</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2182</v>
+        <v>2623</v>
       </c>
       <c r="C4" t="n">
-        <v>6048</v>
+        <v>6262</v>
       </c>
       <c r="D4" t="n">
-        <v>13032</v>
+        <v>13552</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2189</v>
+        <v>2370</v>
       </c>
       <c r="C5" t="n">
-        <v>7006</v>
+        <v>8120</v>
       </c>
       <c r="D5" t="n">
-        <v>7169</v>
+        <v>6807</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1502</v>
+        <v>1496</v>
       </c>
       <c r="C6" t="n">
-        <v>6909</v>
+        <v>8216</v>
       </c>
       <c r="D6" t="n">
-        <v>2596</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>539</v>
+        <v>491</v>
       </c>
       <c r="C7" t="n">
-        <v>5110</v>
+        <v>6034</v>
       </c>
       <c r="D7" t="n">
-        <v>901</v>
+        <v>841</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>2929</v>
+        <v>3288</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1163</v>
+        <v>1218</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6829</v>
+        <v>6528</v>
       </c>
       <c r="C2" t="n">
-        <v>7593</v>
+        <v>11824</v>
       </c>
       <c r="D2" t="n">
-        <v>6559</v>
+        <v>10934</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2068</v>
+        <v>2414</v>
       </c>
       <c r="C2" t="n">
-        <v>3144</v>
+        <v>3174</v>
       </c>
       <c r="D2" t="n">
-        <v>13169</v>
+        <v>12288</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2554</v>
+        <v>3135</v>
       </c>
       <c r="C3" t="n">
-        <v>5315</v>
+        <v>5360</v>
       </c>
       <c r="D3" t="n">
-        <v>15499</v>
+        <v>18403</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3114</v>
+        <v>3508</v>
       </c>
       <c r="C4" t="n">
-        <v>8480</v>
+        <v>8978</v>
       </c>
       <c r="D4" t="n">
-        <v>13355</v>
+        <v>13668</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1448</v>
+        <v>1404</v>
       </c>
       <c r="C5" t="n">
-        <v>9922</v>
+        <v>11749</v>
       </c>
       <c r="D5" t="n">
-        <v>6433</v>
+        <v>6004</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>498</v>
+        <v>453</v>
       </c>
       <c r="C6" t="n">
-        <v>6361</v>
+        <v>7282</v>
       </c>
       <c r="D6" t="n">
-        <v>2040</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>2870</v>
+        <v>3222</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1139</v>
+        <v>1193</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D11" t="n">
         <v>90</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6524</v>
+        <v>8492</v>
       </c>
       <c r="C2" t="n">
-        <v>6295</v>
+        <v>9189</v>
       </c>
       <c r="D2" t="n">
-        <v>16175</v>
+        <v>12824</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2901</v>
+        <v>2773</v>
       </c>
       <c r="C3" t="n">
-        <v>3826</v>
+        <v>5959</v>
       </c>
       <c r="D3" t="n">
-        <v>1741</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4200</v>
+        <v>5438</v>
       </c>
       <c r="C2" t="n">
-        <v>3939</v>
+        <v>6267</v>
       </c>
       <c r="D2" t="n">
-        <v>20664</v>
+        <v>24263</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3872</v>
+        <v>4622</v>
       </c>
       <c r="C3" t="n">
-        <v>4504</v>
+        <v>6715</v>
       </c>
       <c r="D3" t="n">
-        <v>4037</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1294</v>
+        <v>1239</v>
       </c>
       <c r="C4" t="n">
-        <v>2285</v>
+        <v>3535</v>
       </c>
       <c r="D4" t="n">
-        <v>1532</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4801</v>
+        <v>5183</v>
       </c>
       <c r="C2" t="n">
-        <v>6793</v>
+        <v>8420</v>
       </c>
       <c r="D2" t="n">
-        <v>19568</v>
+        <v>25727</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3328</v>
+        <v>4135</v>
       </c>
       <c r="C3" t="n">
-        <v>3631</v>
+        <v>5615</v>
       </c>
       <c r="D3" t="n">
-        <v>6406</v>
+        <v>6978</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2200</v>
+        <v>2449</v>
       </c>
       <c r="C4" t="n">
-        <v>3494</v>
+        <v>5232</v>
       </c>
       <c r="D4" t="n">
-        <v>1966</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="C5" t="n">
-        <v>1344</v>
+        <v>1997</v>
       </c>
       <c r="D5" t="n">
-        <v>1201</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5108</v>
+        <v>5944</v>
       </c>
       <c r="C2" t="n">
-        <v>7199</v>
+        <v>6307</v>
       </c>
       <c r="D2" t="n">
-        <v>26120</v>
+        <v>24722</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3307</v>
+        <v>3809</v>
       </c>
       <c r="C3" t="n">
-        <v>4576</v>
+        <v>6130</v>
       </c>
       <c r="D3" t="n">
-        <v>7955</v>
+        <v>9336</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2363</v>
+        <v>2789</v>
       </c>
       <c r="C4" t="n">
-        <v>3494</v>
+        <v>5325</v>
       </c>
       <c r="D4" t="n">
-        <v>2716</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1143</v>
+        <v>1212</v>
       </c>
       <c r="C5" t="n">
-        <v>2417</v>
+        <v>3582</v>
       </c>
       <c r="D5" t="n">
-        <v>1285</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="C6" t="n">
-        <v>827</v>
+        <v>1146</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>933</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
         <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5797</v>
+        <v>7200</v>
       </c>
       <c r="C2" t="n">
-        <v>6670</v>
+        <v>7426</v>
       </c>
       <c r="D2" t="n">
-        <v>34444</v>
+        <v>37197</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3039</v>
+        <v>3501</v>
       </c>
       <c r="C3" t="n">
-        <v>4846</v>
+        <v>5100</v>
       </c>
       <c r="D3" t="n">
-        <v>9554</v>
+        <v>10252</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1749</v>
+        <v>2040</v>
       </c>
       <c r="C4" t="n">
-        <v>3324</v>
+        <v>4660</v>
       </c>
       <c r="D4" t="n">
-        <v>3131</v>
+        <v>3402</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>924</v>
+        <v>1023</v>
       </c>
       <c r="C5" t="n">
-        <v>2180</v>
+        <v>3257</v>
       </c>
       <c r="D5" t="n">
-        <v>1199</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="C6" t="n">
-        <v>1097</v>
+        <v>1558</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>754</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>372</v>
+        <v>468</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>116</v>
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5695</v>
+        <v>5425</v>
       </c>
       <c r="C2" t="n">
-        <v>4193</v>
+        <v>7744</v>
       </c>
       <c r="D2" t="n">
-        <v>33524</v>
+        <v>27590</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3674</v>
+        <v>4399</v>
       </c>
       <c r="C3" t="n">
-        <v>5089</v>
+        <v>5543</v>
       </c>
       <c r="D3" t="n">
-        <v>13307</v>
+        <v>14024</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2102</v>
+        <v>2390</v>
       </c>
       <c r="C4" t="n">
-        <v>4189</v>
+        <v>4824</v>
       </c>
       <c r="D4" t="n">
-        <v>4300</v>
+        <v>4679</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1186</v>
+        <v>1360</v>
       </c>
       <c r="C5" t="n">
-        <v>2815</v>
+        <v>3997</v>
       </c>
       <c r="D5" t="n">
-        <v>1552</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>591</v>
+        <v>624</v>
       </c>
       <c r="C6" t="n">
-        <v>1707</v>
+        <v>2485</v>
       </c>
       <c r="D6" t="n">
-        <v>829</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C7" t="n">
-        <v>783</v>
+        <v>1066</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>351</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5439</v>
+        <v>6009</v>
       </c>
       <c r="C2" t="n">
-        <v>4518</v>
+        <v>6055</v>
       </c>
       <c r="D2" t="n">
-        <v>27317</v>
+        <v>28154</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3828</v>
+        <v>4026</v>
       </c>
       <c r="C3" t="n">
-        <v>3982</v>
+        <v>5819</v>
       </c>
       <c r="D3" t="n">
-        <v>15583</v>
+        <v>15098</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2465</v>
+        <v>2861</v>
       </c>
       <c r="C4" t="n">
-        <v>4611</v>
+        <v>5117</v>
       </c>
       <c r="D4" t="n">
-        <v>5898</v>
+        <v>6196</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1451</v>
+        <v>1640</v>
       </c>
       <c r="C5" t="n">
-        <v>3481</v>
+        <v>4312</v>
       </c>
       <c r="D5" t="n">
-        <v>1991</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>804</v>
+        <v>881</v>
       </c>
       <c r="C6" t="n">
-        <v>2282</v>
+        <v>3240</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C7" t="n">
-        <v>1271</v>
+        <v>1788</v>
       </c>
       <c r="D7" t="n">
-        <v>593</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>547</v>
+        <v>701</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_21_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_21_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6767</v>
+        <v>989</v>
       </c>
       <c r="C2" t="n">
-        <v>13585</v>
+        <v>4952</v>
       </c>
       <c r="D2" t="n">
-        <v>28623</v>
+        <v>21411</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4070</v>
+        <v>1616</v>
       </c>
       <c r="C3" t="n">
-        <v>5200</v>
+        <v>10242</v>
       </c>
       <c r="D3" t="n">
-        <v>15939</v>
+        <v>15800</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2888</v>
+        <v>1113</v>
       </c>
       <c r="C4" t="n">
-        <v>5311</v>
+        <v>11943</v>
       </c>
       <c r="D4" t="n">
-        <v>7545</v>
+        <v>5962</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1917</v>
+        <v>581</v>
       </c>
       <c r="C5" t="n">
-        <v>4616</v>
+        <v>8478</v>
       </c>
       <c r="D5" t="n">
-        <v>2717</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1117</v>
+        <v>245</v>
       </c>
       <c r="C6" t="n">
-        <v>3679</v>
+        <v>3385</v>
       </c>
       <c r="D6" t="n">
-        <v>1139</v>
+        <v>715</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>520</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>2470</v>
+        <v>1014</v>
       </c>
       <c r="D7" t="n">
-        <v>645</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>191</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>1190</v>
+        <v>361</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>454</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6721</v>
+        <v>925</v>
       </c>
       <c r="C2" t="n">
-        <v>12777</v>
+        <v>6430</v>
       </c>
       <c r="D2" t="n">
-        <v>29850</v>
+        <v>18818</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4246</v>
+        <v>1146</v>
       </c>
       <c r="C3" t="n">
-        <v>7812</v>
+        <v>6819</v>
       </c>
       <c r="D3" t="n">
-        <v>16516</v>
+        <v>15520</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2912</v>
+        <v>1147</v>
       </c>
       <c r="C4" t="n">
-        <v>5149</v>
+        <v>10845</v>
       </c>
       <c r="D4" t="n">
-        <v>8532</v>
+        <v>7480</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2050</v>
+        <v>717</v>
       </c>
       <c r="C5" t="n">
-        <v>4782</v>
+        <v>9964</v>
       </c>
       <c r="D5" t="n">
-        <v>3375</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1315</v>
+        <v>350</v>
       </c>
       <c r="C6" t="n">
-        <v>4049</v>
+        <v>5731</v>
       </c>
       <c r="D6" t="n">
-        <v>1340</v>
+        <v>868</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>683</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>2954</v>
+        <v>2069</v>
       </c>
       <c r="D7" t="n">
-        <v>711</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>286</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1716</v>
+        <v>633</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>737</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>309</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
         <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8676</v>
+        <v>519</v>
       </c>
       <c r="C2" t="n">
-        <v>13248</v>
+        <v>2969</v>
       </c>
       <c r="D2" t="n">
-        <v>40760</v>
+        <v>12977</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4250</v>
+        <v>1051</v>
       </c>
       <c r="C3" t="n">
-        <v>8670</v>
+        <v>6466</v>
       </c>
       <c r="D3" t="n">
-        <v>17059</v>
+        <v>15516</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2914</v>
+        <v>1249</v>
       </c>
       <c r="C4" t="n">
-        <v>6091</v>
+        <v>10307</v>
       </c>
       <c r="D4" t="n">
-        <v>9422</v>
+        <v>8406</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2118</v>
+        <v>714</v>
       </c>
       <c r="C5" t="n">
-        <v>4830</v>
+        <v>11666</v>
       </c>
       <c r="D5" t="n">
-        <v>3933</v>
+        <v>2668</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1470</v>
+        <v>272</v>
       </c>
       <c r="C6" t="n">
-        <v>4256</v>
+        <v>6558</v>
       </c>
       <c r="D6" t="n">
-        <v>1596</v>
+        <v>878</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>824</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>3342</v>
+        <v>1800</v>
       </c>
       <c r="D7" t="n">
-        <v>776</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>380</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>2159</v>
+        <v>500</v>
       </c>
       <c r="D8" t="n">
-        <v>476</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1091</v>
+        <v>225</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>452</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>223</v>
+        <v>123</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7963</v>
+        <v>437</v>
       </c>
       <c r="C2" t="n">
-        <v>9326</v>
+        <v>3597</v>
       </c>
       <c r="D2" t="n">
-        <v>33426</v>
+        <v>11193</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5089</v>
+        <v>707</v>
       </c>
       <c r="C3" t="n">
-        <v>12226</v>
+        <v>4315</v>
       </c>
       <c r="D3" t="n">
-        <v>18452</v>
+        <v>14128</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1957</v>
+        <v>1039</v>
       </c>
       <c r="C4" t="n">
-        <v>7852</v>
+        <v>8347</v>
       </c>
       <c r="D4" t="n">
-        <v>8906</v>
+        <v>9391</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1358</v>
+        <v>831</v>
       </c>
       <c r="C5" t="n">
-        <v>4170</v>
+        <v>10922</v>
       </c>
       <c r="D5" t="n">
-        <v>2583</v>
+        <v>3413</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>761</v>
+        <v>394</v>
       </c>
       <c r="C6" t="n">
-        <v>3275</v>
+        <v>8719</v>
       </c>
       <c r="D6" t="n">
-        <v>760</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>2115</v>
+        <v>3746</v>
       </c>
       <c r="D7" t="n">
-        <v>466</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1069</v>
+        <v>985</v>
       </c>
       <c r="D8" t="n">
-        <v>319</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>442</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>243</v>
+        <v>362</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D11" t="n">
-        <v>157</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>64</v>
+      </c>
+      <c r="D15" t="n">
         <v>49</v>
-      </c>
-      <c r="D15" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4716</v>
+        <v>329</v>
       </c>
       <c r="C2" t="n">
-        <v>4280</v>
+        <v>2857</v>
       </c>
       <c r="D2" t="n">
-        <v>22746</v>
+        <v>9561</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5432</v>
+        <v>544</v>
       </c>
       <c r="C3" t="n">
-        <v>9993</v>
+        <v>3656</v>
       </c>
       <c r="D3" t="n">
-        <v>19335</v>
+        <v>13007</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2671</v>
+        <v>862</v>
       </c>
       <c r="C4" t="n">
-        <v>9846</v>
+        <v>6749</v>
       </c>
       <c r="D4" t="n">
-        <v>10180</v>
+        <v>9832</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1487</v>
+        <v>871</v>
       </c>
       <c r="C5" t="n">
-        <v>5732</v>
+        <v>10174</v>
       </c>
       <c r="D5" t="n">
-        <v>3282</v>
+        <v>4063</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>895</v>
+        <v>472</v>
       </c>
       <c r="C6" t="n">
-        <v>3736</v>
+        <v>9763</v>
       </c>
       <c r="D6" t="n">
-        <v>930</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>325</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>2596</v>
+        <v>5219</v>
       </c>
       <c r="D7" t="n">
-        <v>509</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1376</v>
+        <v>1529</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>479</v>
+        <v>376</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>207</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4743</v>
+        <v>574</v>
       </c>
       <c r="C2" t="n">
-        <v>8790</v>
+        <v>6480</v>
       </c>
       <c r="D2" t="n">
-        <v>30446</v>
+        <v>12657</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4323</v>
+        <v>394</v>
       </c>
       <c r="C3" t="n">
-        <v>6604</v>
+        <v>2993</v>
       </c>
       <c r="D3" t="n">
-        <v>18685</v>
+        <v>11761</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3284</v>
+        <v>651</v>
       </c>
       <c r="C4" t="n">
-        <v>9710</v>
+        <v>5302</v>
       </c>
       <c r="D4" t="n">
-        <v>11179</v>
+        <v>9990</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1748</v>
+        <v>805</v>
       </c>
       <c r="C5" t="n">
-        <v>7524</v>
+        <v>8581</v>
       </c>
       <c r="D5" t="n">
-        <v>4241</v>
+        <v>4714</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1037</v>
+        <v>563</v>
       </c>
       <c r="C6" t="n">
-        <v>4544</v>
+        <v>9838</v>
       </c>
       <c r="D6" t="n">
-        <v>1256</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>475</v>
+        <v>199</v>
       </c>
       <c r="C7" t="n">
-        <v>3089</v>
+        <v>6909</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>159</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>1855</v>
+        <v>2845</v>
       </c>
       <c r="D8" t="n">
-        <v>348</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>799</v>
+        <v>752</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>316</v>
+        <v>262</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2877</v>
+        <v>408</v>
       </c>
       <c r="C2" t="n">
-        <v>4321</v>
+        <v>3680</v>
       </c>
       <c r="D2" t="n">
-        <v>21263</v>
+        <v>9316</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4302</v>
+        <v>596</v>
       </c>
       <c r="C3" t="n">
-        <v>7053</v>
+        <v>4060</v>
       </c>
       <c r="D3" t="n">
-        <v>19668</v>
+        <v>12771</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3558</v>
+        <v>1065</v>
       </c>
       <c r="C4" t="n">
-        <v>9579</v>
+        <v>8124</v>
       </c>
       <c r="D4" t="n">
-        <v>12033</v>
+        <v>10050</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1815</v>
+        <v>542</v>
       </c>
       <c r="C5" t="n">
-        <v>9133</v>
+        <v>13232</v>
       </c>
       <c r="D5" t="n">
-        <v>4352</v>
+        <v>4197</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>841</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>5373</v>
+        <v>8699</v>
       </c>
       <c r="D6" t="n">
-        <v>1220</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>3258</v>
+        <v>2788</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>1310</v>
+        <v>736</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>256</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3731</v>
+        <v>239</v>
       </c>
       <c r="C2" t="n">
-        <v>7012</v>
+        <v>2262</v>
       </c>
       <c r="D2" t="n">
-        <v>24488</v>
+        <v>7384</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3206</v>
+        <v>442</v>
       </c>
       <c r="C3" t="n">
-        <v>5247</v>
+        <v>3483</v>
       </c>
       <c r="D3" t="n">
-        <v>18581</v>
+        <v>11524</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3356</v>
+        <v>721</v>
       </c>
       <c r="C4" t="n">
-        <v>8331</v>
+        <v>5828</v>
       </c>
       <c r="D4" t="n">
-        <v>12839</v>
+        <v>9732</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2204</v>
+        <v>521</v>
       </c>
       <c r="C5" t="n">
-        <v>9131</v>
+        <v>9766</v>
       </c>
       <c r="D5" t="n">
-        <v>5367</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1085</v>
+        <v>176</v>
       </c>
       <c r="C6" t="n">
-        <v>6947</v>
+        <v>8553</v>
       </c>
       <c r="D6" t="n">
-        <v>1595</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>302</v>
+        <v>42</v>
       </c>
       <c r="C7" t="n">
-        <v>4076</v>
+        <v>3619</v>
       </c>
       <c r="D7" t="n">
-        <v>633</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2003</v>
+        <v>901</v>
       </c>
       <c r="D8" t="n">
-        <v>391</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>622</v>
+        <v>244</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2580</v>
+        <v>163</v>
       </c>
       <c r="C2" t="n">
-        <v>4753</v>
+        <v>4273</v>
       </c>
       <c r="D2" t="n">
-        <v>18282</v>
+        <v>9327</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2951</v>
+        <v>296</v>
       </c>
       <c r="C3" t="n">
-        <v>5428</v>
+        <v>2533</v>
       </c>
       <c r="D3" t="n">
-        <v>18261</v>
+        <v>10134</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3052</v>
+        <v>521</v>
       </c>
       <c r="C4" t="n">
-        <v>7163</v>
+        <v>4491</v>
       </c>
       <c r="D4" t="n">
-        <v>13288</v>
+        <v>9745</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2384</v>
+        <v>551</v>
       </c>
       <c r="C5" t="n">
-        <v>9022</v>
+        <v>7597</v>
       </c>
       <c r="D5" t="n">
-        <v>6095</v>
+        <v>5094</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1254</v>
+        <v>291</v>
       </c>
       <c r="C6" t="n">
-        <v>7852</v>
+        <v>9130</v>
       </c>
       <c r="D6" t="n">
-        <v>1897</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>268</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>4972</v>
+        <v>5925</v>
       </c>
       <c r="D7" t="n">
-        <v>709</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>2485</v>
+        <v>2072</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>657</v>
+        <v>516</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3265</v>
+        <v>317</v>
       </c>
       <c r="C2" t="n">
-        <v>5362</v>
+        <v>12058</v>
       </c>
       <c r="D2" t="n">
-        <v>16517</v>
+        <v>10476</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2386</v>
+        <v>202</v>
       </c>
       <c r="C3" t="n">
-        <v>4671</v>
+        <v>2915</v>
       </c>
       <c r="D3" t="n">
-        <v>17123</v>
+        <v>9343</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2623</v>
+        <v>374</v>
       </c>
       <c r="C4" t="n">
-        <v>6262</v>
+        <v>3476</v>
       </c>
       <c r="D4" t="n">
-        <v>13552</v>
+        <v>9512</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2370</v>
+        <v>493</v>
       </c>
       <c r="C5" t="n">
-        <v>8120</v>
+        <v>5964</v>
       </c>
       <c r="D5" t="n">
-        <v>6807</v>
+        <v>5653</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1496</v>
+        <v>360</v>
       </c>
       <c r="C6" t="n">
-        <v>8216</v>
+        <v>8365</v>
       </c>
       <c r="D6" t="n">
-        <v>2338</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>491</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>6034</v>
+        <v>7304</v>
       </c>
       <c r="D7" t="n">
-        <v>841</v>
+        <v>847</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c r="C8" t="n">
-        <v>3288</v>
+        <v>3657</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>1218</v>
+        <v>1120</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>341</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6528</v>
+        <v>4619</v>
       </c>
       <c r="C2" t="n">
-        <v>11824</v>
+        <v>20164</v>
       </c>
       <c r="D2" t="n">
-        <v>10934</v>
+        <v>7922</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2414</v>
+        <v>167</v>
       </c>
       <c r="C2" t="n">
-        <v>3174</v>
+        <v>23978</v>
       </c>
       <c r="D2" t="n">
-        <v>12288</v>
+        <v>18535</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3135</v>
+        <v>202</v>
       </c>
       <c r="C3" t="n">
-        <v>5360</v>
+        <v>5811</v>
       </c>
       <c r="D3" t="n">
-        <v>18403</v>
+        <v>8881</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3508</v>
+        <v>270</v>
       </c>
       <c r="C4" t="n">
-        <v>8978</v>
+        <v>3133</v>
       </c>
       <c r="D4" t="n">
-        <v>13668</v>
+        <v>9198</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1404</v>
+        <v>412</v>
       </c>
       <c r="C5" t="n">
-        <v>11749</v>
+        <v>4812</v>
       </c>
       <c r="D5" t="n">
-        <v>6004</v>
+        <v>5945</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>453</v>
+        <v>377</v>
       </c>
       <c r="C6" t="n">
-        <v>7282</v>
+        <v>7266</v>
       </c>
       <c r="D6" t="n">
-        <v>1847</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>3222</v>
+        <v>7716</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>1193</v>
+        <v>4977</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>334</v>
+        <v>2039</v>
       </c>
       <c r="D9" t="n">
-        <v>175</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>146</v>
+        <v>576</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>84</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8492</v>
+        <v>4154</v>
       </c>
       <c r="C2" t="n">
-        <v>9189</v>
+        <v>20410</v>
       </c>
       <c r="D2" t="n">
-        <v>12824</v>
+        <v>19223</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2773</v>
+        <v>1490</v>
       </c>
       <c r="C3" t="n">
-        <v>5959</v>
+        <v>7962</v>
       </c>
       <c r="D3" t="n">
-        <v>2476</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5438</v>
+        <v>2603</v>
       </c>
       <c r="C2" t="n">
-        <v>6267</v>
+        <v>9062</v>
       </c>
       <c r="D2" t="n">
-        <v>24263</v>
+        <v>18593</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4622</v>
+        <v>2357</v>
       </c>
       <c r="C3" t="n">
-        <v>6715</v>
+        <v>13201</v>
       </c>
       <c r="D3" t="n">
-        <v>4032</v>
+        <v>4657</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1239</v>
+        <v>702</v>
       </c>
       <c r="C4" t="n">
-        <v>3535</v>
+        <v>4940</v>
       </c>
       <c r="D4" t="n">
-        <v>1680</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5183</v>
+        <v>1814</v>
       </c>
       <c r="C2" t="n">
-        <v>8420</v>
+        <v>12204</v>
       </c>
       <c r="D2" t="n">
-        <v>25727</v>
+        <v>26253</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4135</v>
+        <v>2046</v>
       </c>
       <c r="C3" t="n">
-        <v>5615</v>
+        <v>9364</v>
       </c>
       <c r="D3" t="n">
-        <v>6978</v>
+        <v>6655</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2449</v>
+        <v>1329</v>
       </c>
       <c r="C4" t="n">
-        <v>5232</v>
+        <v>9674</v>
       </c>
       <c r="D4" t="n">
-        <v>2080</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>559</v>
+        <v>342</v>
       </c>
       <c r="C5" t="n">
-        <v>1997</v>
+        <v>2884</v>
       </c>
       <c r="D5" t="n">
-        <v>1249</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>264</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>356</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5944</v>
+        <v>1300</v>
       </c>
       <c r="C2" t="n">
-        <v>6307</v>
+        <v>7281</v>
       </c>
       <c r="D2" t="n">
-        <v>24722</v>
+        <v>33822</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3809</v>
+        <v>1605</v>
       </c>
       <c r="C3" t="n">
-        <v>6130</v>
+        <v>9430</v>
       </c>
       <c r="D3" t="n">
-        <v>9336</v>
+        <v>9165</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2789</v>
+        <v>1430</v>
       </c>
       <c r="C4" t="n">
-        <v>5325</v>
+        <v>9303</v>
       </c>
       <c r="D4" t="n">
-        <v>2910</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1212</v>
+        <v>697</v>
       </c>
       <c r="C5" t="n">
-        <v>3582</v>
+        <v>6409</v>
       </c>
       <c r="D5" t="n">
-        <v>1354</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>302</v>
+        <v>198</v>
       </c>
       <c r="C6" t="n">
-        <v>1146</v>
+        <v>1594</v>
       </c>
       <c r="D6" t="n">
-        <v>933</v>
+        <v>826</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>297</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>375</v>
+        <v>303</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7200</v>
+        <v>2519</v>
       </c>
       <c r="C2" t="n">
-        <v>7426</v>
+        <v>5189</v>
       </c>
       <c r="D2" t="n">
-        <v>37197</v>
+        <v>31680</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3501</v>
+        <v>1223</v>
       </c>
       <c r="C3" t="n">
-        <v>5100</v>
+        <v>7374</v>
       </c>
       <c r="D3" t="n">
-        <v>10252</v>
+        <v>12085</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2040</v>
+        <v>1308</v>
       </c>
       <c r="C4" t="n">
-        <v>4660</v>
+        <v>9083</v>
       </c>
       <c r="D4" t="n">
-        <v>3402</v>
+        <v>3825</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1023</v>
+        <v>891</v>
       </c>
       <c r="C5" t="n">
-        <v>3257</v>
+        <v>7692</v>
       </c>
       <c r="D5" t="n">
-        <v>1281</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="C6" t="n">
-        <v>1558</v>
+        <v>3842</v>
       </c>
       <c r="D6" t="n">
-        <v>754</v>
+        <v>881</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>468</v>
+        <v>891</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>270</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5425</v>
+        <v>1860</v>
       </c>
       <c r="C2" t="n">
-        <v>7744</v>
+        <v>17735</v>
       </c>
       <c r="D2" t="n">
-        <v>27590</v>
+        <v>37560</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4399</v>
+        <v>1431</v>
       </c>
       <c r="C3" t="n">
-        <v>5543</v>
+        <v>5673</v>
       </c>
       <c r="D3" t="n">
-        <v>14024</v>
+        <v>13800</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2390</v>
+        <v>1096</v>
       </c>
       <c r="C4" t="n">
-        <v>4824</v>
+        <v>8019</v>
       </c>
       <c r="D4" t="n">
-        <v>4679</v>
+        <v>4940</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1360</v>
+        <v>953</v>
       </c>
       <c r="C5" t="n">
-        <v>3997</v>
+        <v>8159</v>
       </c>
       <c r="D5" t="n">
-        <v>1636</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>624</v>
+        <v>526</v>
       </c>
       <c r="C6" t="n">
-        <v>2485</v>
+        <v>5431</v>
       </c>
       <c r="D6" t="n">
-        <v>844</v>
+        <v>941</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>1066</v>
+        <v>2163</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>351</v>
+        <v>543</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>207</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6009</v>
+        <v>1768</v>
       </c>
       <c r="C2" t="n">
-        <v>6055</v>
+        <v>11776</v>
       </c>
       <c r="D2" t="n">
-        <v>28154</v>
+        <v>30277</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4026</v>
+        <v>1872</v>
       </c>
       <c r="C3" t="n">
-        <v>5819</v>
+        <v>10937</v>
       </c>
       <c r="D3" t="n">
-        <v>15098</v>
+        <v>14488</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2861</v>
+        <v>880</v>
       </c>
       <c r="C4" t="n">
-        <v>5117</v>
+        <v>12451</v>
       </c>
       <c r="D4" t="n">
-        <v>6196</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1640</v>
+        <v>486</v>
       </c>
       <c r="C5" t="n">
-        <v>4312</v>
+        <v>5322</v>
       </c>
       <c r="D5" t="n">
-        <v>2141</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>881</v>
+        <v>188</v>
       </c>
       <c r="C6" t="n">
-        <v>3240</v>
+        <v>2119</v>
       </c>
       <c r="D6" t="n">
-        <v>960</v>
+        <v>629</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>355</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>1788</v>
+        <v>532</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>701</v>
+        <v>273</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>272</v>
+        <v>228</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>148</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
